--- a/output/robotics_buyers.xlsx
+++ b/output/robotics_buyers.xlsx
@@ -7,10 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Robotics &amp; Automatio" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Robotics &amp; Automation" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Scoring Rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robotics &amp; Automatio'!$A$1:$G$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robotics &amp; Automation'!$A$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,8 +33,11 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -50,6 +54,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
         <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
@@ -77,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -91,6 +101,10 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -456,16 +470,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="35" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="8" max="8"/>
+    <col width="45" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -476,312 +492,402 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Buyer Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Why Buy</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Why Buy from China</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>China Purchase History</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LinkedIn Search</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Foxconn (Hon Hai Precision Industry Co., Ltd.)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Automotive manufacturer</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="n">
-        <v>90</v>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.foxconn.com</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Electronics manufacturer</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>95</v>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>High volume assembly lines require cost-effective robots for welding, painting, and material handling, where Chinese OEMs offer aggressive pricing.</t>
+          <t>Taiwan (HQ) / US operations</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ford%20Motor%20Company</t>
+          <t>Already a major buyer of automation and has publicly deployed Chinese robots in their factories for cost reduction.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Yes - Foxconn has used robots from Chinese vendors like Siasun and Estun in various facilities.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Foxconn</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>DHL Supply Chain</t>
+          <t>KUKA AG</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Warehouse &amp; 3PL logistics operator</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="n">
+          <t>https://www.kuka.com</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>System integrator</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="n">
         <v>90</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>They aggressively deploy autonomous mobile robots (AMRs) from Chinese vendors to cut fulfillment costs.</t>
-        </is>
-      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=DHL%20Supply%20Chain</t>
+          <t>As a major integrator, they already source robots globally and have partnerships with Chinese manufacturers like Midea (their parent).</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Yes - KUKA is owned by Midea Group (Chinese) and integrates Chinese robots in some solutions.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=KUKA%20AG</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Magna International Inc.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Automotive Tier 1 parts supplier</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>88</v>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.ford.com</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Automotive OEM</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>85</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>As a parts supplier with thin margins, they seek lower-cost automation for stamping and assembly lines.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Magna%20International%20Inc.</t>
+          <t>High-volume manufacturing with intense cost pressure and a history of sourcing global automation to stay competitive.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Ford%20Motor%20Company</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Volkswagen AG</t>
+          <t>Magna International Inc.</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Automotive manufacturer</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.magna.com</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 supplier</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>82</v>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Under cost pressure in EV transition, they are open to second-tier automation suppliers for non-critical stations.</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Volkswagen%20AG</t>
+          <t>Global Tier 1 with thin margins and high volume, constantly seeking lower-cost automation for assembly and welding.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Magna%20International%20Inc.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>XPO Logistics, Inc.</t>
+          <t>Volkswagen AG</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Warehouse &amp; 3PL logistics operator</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.volkswagenag.com</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Automotive OEM</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Their warehouses need low-cost robotic sortation and palletizing systems to compete with Amazon.</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=XPO%20Logistics%2C%20Inc.</t>
+          <t>Massive global production footprint and ongoing EV transition require cost-effective automation solutions.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Volkswagen%20AG</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Lincoln Electric Holdings, Inc.</t>
+          <t>Samsung Electronics Co., Ltd.</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Metal fabrication &amp; welding shops</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>85</v>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.samsung.com</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Electronics manufacturer</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>80</v>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>As a welding equipment maker, they are integrating Chinese robotic arms into their automated welding systems for SMEs.</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Lincoln%20Electric%20Holdings%2C%20Inc.</t>
+          <t>High-volume electronics assembly with extreme cost sensitivity and existing supply chain ties to China.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Samsung%20Electronics%20Co.%2C%20Ltd.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Tyson Foods, Inc.</t>
+          <t>Robert Bosch GmbH</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Food &amp; beverage processing plants</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.bosch.com</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Tier 1 supplier</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>78</v>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Labor shortages in meat processing push them to adopt Chinese collaborative robots for cutting and packing.</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tyson%20Foods%2C%20Inc.</t>
+          <t>Diverse manufacturing operations and cost optimization initiatives make them a candidate for Chinese robots in secondary processes.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Robert%20Bosch%20GmbH</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Hyundai Mobis</t>
+          <t>General Motors Company</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Automotive Tier 1 parts supplier</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>80</v>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.gm.com</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Automotive OEM</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>78</v>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>They are actively testing Chinese collaborative robots for electronics assembly in their EV parts plants.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hyundai%20Mobis</t>
+          <t>GM's aggressive EV investment and cost-cutting initiatives make them a strong candidate for lower-cost Chinese robots in body shops.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=General%20Motors%20Company</t>
         </is>
       </c>
     </row>
@@ -793,28 +899,38 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Automotive manufacturer</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
+          <t>https://global.toyota</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Automotive OEM</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="n">
         <v>75</v>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>While traditionally conservative, their global plants in emerging markets increasingly trial Chinese robots for simple tasks.</t>
-        </is>
-      </c>
       <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Lean manufacturing and cost discipline make them open to competitive Chinese robotics for non-core tasks.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/companies/?keywords=Toyota%20Motor%20Corporation</t>
         </is>
@@ -823,315 +939,405 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Aisin Corporation</t>
+          <t>Tyson Foods, Inc.</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Automotive Tier 1 parts supplier</t>
-        </is>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>72</v>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.tysonfoods.com</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Food processing</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>75</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>They are expanding production in Southeast Asia and may use Chinese robots for simple assembly tasks.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Aisin%20Corporation</t>
+          <t>Labor shortages and high turnover in meat processing push them to adopt affordable automation, including Chinese robots.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Tyson%20Foods%2C%20Inc.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Bosch Rexroth AG</t>
+          <t>Nestlé S.A.</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Automation system integrator &amp; robot distributor</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.nestle.com</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Food processing</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>72</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>They may resell Chinese robots for price-sensitive customers in Eastern Europe and Asia.</t>
+          <t>Switzerland (US operations)</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Bosch%20Rexroth%20AG</t>
+          <t>Food packaging and palletizing are repetitive tasks where Chinese robots offer significant cost savings over European brands.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Nestl%C3%A9%20S.A.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Nestlé S.A.</t>
+          <t>Hyundai Motor Company</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Food &amp; beverage processing plants</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>70</v>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.hyundai.com</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Automotive OEM</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>72</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Switzerland (but major US operations)</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>They are replacing manual packaging lines with Chinese robots in their North American plants.</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nestl%C3%A9%20S.A.</t>
+          <t>Korean automakers face cost competition and have been increasing automation in their plants, with potential to test Chinese robots.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Hyundai%20Motor%20Company</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Samsung Electronics Co., Ltd.</t>
+          <t>DHL Supply Chain</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Electronics manufacturer (PCB assembly, semiconductor fabs)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>65</v>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.dhl.com</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3PL logistics</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>70</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>For secondary operations like packaging and material transport, they evaluate Chinese AMRs and SCARA robots.</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Samsung%20Electronics%20Co.%2C%20Ltd.</t>
+          <t>Warehouse automation is a priority, and Chinese AMRs and robotic arms offer cost-effective solutions for sorting and packing.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=DHL%20Supply%20Chain</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>LG Electronics Inc.</t>
+          <t>Nucor Corporation</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Electronics manufacturer (PCB assembly)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.nucor.com</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Metal fab</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>70</v>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>They are diversifying robot suppliers for display assembly and logistics in their factories.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=LG%20Electronics%20Inc.</t>
+          <t>Steel processing and material handling require robust robots, and Chinese vendors offer competitive pricing for high-volume use.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Nucor%20Corporation</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Siemens AG</t>
+          <t>ThyssenKrupp AG</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Automation system integrator &amp; robot distributor</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="n">
-        <v>60</v>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.thyssenkrupp.com</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Metal fab</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>Germany</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>They integrate third-party robots into their digital factory solutions, including Chinese brands for cost-sensitive clients.</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Siemens%20AG</t>
+          <t>Heavy metal fabrication and welding tasks are ideal for cost-effective Chinese industrial robots.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=ThyssenKrupp%20AG</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>KUKA AG</t>
+          <t>XPO Logistics, Inc.</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Automation system integrator &amp; robot distributor</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.xpo.com</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3PL logistics</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>As a competitor, they might source certain components or low-end robots from China for specific projects.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=KUKA%20AG</t>
+          <t>Large-scale distribution centers need affordable robotic palletizing and picking solutions to compete with rivals.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=XPO%20Logistics%2C%20Inc.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>GSK plc (GlaxoSmithKline)</t>
+          <t>Rockwell Automation, Inc.</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Pharmaceutical manufacturer</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>55</v>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.rockwellautomation.com</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>System integrator</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>65</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>For non-sterile packaging and warehouse automation, they consider Chinese robots to reduce costs.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=GSK%20plc</t>
+          <t>They provide automation solutions and may integrate Chinese robots for cost-sensitive clients in North America.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Rockwell%20Automation%2C%20Inc.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Yaskawa Electric Corporation</t>
+          <t>FANUC Corporation</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Automation system integrator &amp; robot distributor</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.fanuc.com</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>System integrator</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>60</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>They may partner with Chinese manufacturers for low-cost servo motors or simple robot arms.</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Yaskawa%20Electric%20Corporation</t>
+          <t>They are a competitor, but they also buy components and could source Chinese robots for low-end applications in Asia.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=FANUC%20Corporation</t>
         </is>
       </c>
     </row>
@@ -1143,28 +1349,38 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Pharmaceutical manufacturer</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.pfizer.com</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>55</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>They are cautious but may use Chinese robots for secondary packaging lines in their global plants.</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Pharma automation is highly regulated, but secondary packaging and logistics could use Chinese robots for cost savings.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>https://www.linkedin.com/search/results/companies/?keywords=Pfizer%20Inc.</t>
         </is>
@@ -1173,40 +1389,128 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Fanuc Corporation</t>
+          <t>Novartis International AG</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Automation system integrator &amp; robot distributor</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="n">
-        <v>45</v>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
+          <t>https://www.novartis.com</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Pharma</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>50</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Enterprise (&gt;1000)</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Unlikely to buy complete robots, but could source Chinese components for their lower-tier models.</t>
+          <t>Switzerland (US operations)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Fanuc%20Corporation</t>
+          <t>Regulatory hurdles limit core production, but warehouse and lab automation could see Chinese robot adoption.</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>No - no public record</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/search/results/companies/?keywords=Novartis%20International%20AG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:I21"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Score Range</t>
+        </is>
+      </c>
+      <c r="B1" s="6" t="inlineStr">
+        <is>
+          <t>Definition</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>90-95</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Actively deploying, large scale, public RFQ or known to evaluate Chinese vendors</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>75-89</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Strong fit - industry + scale + cost pressure align</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>55-74</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Moderate fit - possible buyer but not urgent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>40-54</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Weak fit - could buy but unlikely to prioritize Chinese</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/robotics_buyers.xlsx
+++ b/output/robotics_buyers.xlsx
@@ -517,17 +517,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Why Buy from China</t>
+          <t>Why Buy</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>China Purchase History</t>
+          <t>China Purchase</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>LinkedIn Search</t>
+          <t>LinkedIn</t>
         </is>
       </c>
     </row>
@@ -1446,14 +1446,14 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Score Range</t>
+          <t>Score</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Actively deploying, large scale, public RFQ or known to evaluate Chinese vendors</t>
+          <t>Top-tier buyer — large scale, known to source from China</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Strong fit - industry + scale + cost pressure align</t>
+          <t>Strong fit — cost-sensitive, growing demand</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Moderate fit - possible buyer but not urgent</t>
+          <t>Moderate fit — possible buyer</t>
         </is>
       </c>
     </row>
@@ -1506,7 +1506,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Weak fit - could buy but unlikely to prioritize Chinese</t>
+          <t>Weak fit — niche or occasional</t>
         </is>
       </c>
     </row>

--- a/output/robotics_buyers.xlsx
+++ b/output/robotics_buyers.xlsx
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Top-tier buyer — large scale, known to source from China</t>
+          <t>Top-tier — large scale, known to source from China</t>
         </is>
       </c>
     </row>

--- a/output/robotics_buyers.xlsx
+++ b/output/robotics_buyers.xlsx
@@ -8,10 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="Robotics &amp; Automation" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Scoring Rubric" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robotics &amp; Automation'!$A$1:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Robotics &amp; Automation'!$A$1:$S$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,9 +31,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -52,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C6EFCE"/>
-        <bgColor rgb="00C6EFCE"/>
+        <fgColor rgb="00D5E8D4"/>
+        <bgColor rgb="00D5E8D4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D5E8D4"/>
-        <bgColor rgb="00D5E8D4"/>
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
     <fill>
@@ -87,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -104,7 +100,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -470,24 +465,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
-    <col width="45" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="35" customWidth="1" min="9" max="9"/>
+    <col width="25" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
+    <col width="20" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="8" customWidth="1" min="18" max="18"/>
+    <col width="25" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Company Name</t>
+          <t>Company</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -497,37 +502,87 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Founded</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Headquarters</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Employees</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Procurement Needs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Partner Profile</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Key Markets</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>China Presence</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Competitors</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Market Share</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Recent News</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>Buyer Type</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Size</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Relevance</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Size</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Why Buy</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>China Purchase</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>LinkedIn</t>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Why</t>
         </is>
       </c>
     </row>
@@ -544,35 +599,85 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>新北市，中国台湾</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>800000</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1800亿美元</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>全球最大电子代工服务商，为苹果等品牌提供iPhone、服务器、游戏机等产品的组装制造服务。</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>大规模采购用于3C装配的六轴机器人、协作机器人、自动化测试设备及智能仓储物流系统。</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>偏好能提供整线自动化解决方案、具备快速响应能力、成本控制优秀的中国设备供应商。</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>中国大陆、美国、印度、越南、墨西哥</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>深圳、郑州、成都、烟台等数十个制造园区</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Pegatron, Quanta Computer, Compal Electronics</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>全球电子代工市场份额约30%</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在印度泰米尔纳德邦扩建iPhone产线，同步引入自动化组装机器人。</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
           <t>Electronics manufacturer</t>
         </is>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan (HQ) / US operations</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="n">
         <v>95</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan (HQ) / US operations</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Already a major buyer of automation and has publicly deployed Chinese robots in their factories for cost reduction.</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>Yes - Foxconn has used robots from Chinese vendors like Siasun and Estun in various facilities.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Foxconn</t>
         </is>
       </c>
     </row>
@@ -589,35 +694,85 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>1898</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>奥格斯堡，德国</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>约40亿欧元</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的工业机器人及自动化解决方案供应商，提供机器人本体、控制器、软件及系统集成服务，广泛应用于汽车、电子、消费品等行业。</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购高性价比的机器人零部件（减速器、伺服电机、传感器）、机器人本体代工、以及自动化产线配套设备。</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备精密制造能力、通过ISO认证、有机器人行业配套经验的中国供应商，能提供稳定批量供货和快速响应技术支持。</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>德国、中国、美国、韩国、意大利</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>库卡机器人（上海）有限公司，中国区总部及制造基地（佛山）</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>ABB、发那科、安川电机</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>全球工业机器人市场份额约10%，中国市场份额约12%（外资品牌中前三）。</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布与美的集团协同，在顺德新建机器人超级工厂，产能提升至10万台/年。</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
           <t>System integrator</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="n">
         <v>90</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="S3" s="2" t="inlineStr">
         <is>
           <t>As a major integrator, they already source robots globally and have partnerships with Chinese manufacturers like Midea (their parent).</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>Yes - KUKA is owned by Midea Group (Chinese) and integrates Chinese robots in some solutions.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=KUKA%20AG</t>
         </is>
       </c>
     </row>
@@ -634,35 +789,85 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>迪尔伯恩，美国</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>177000</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1762亿美元</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的汽车制造商，生产销售福特和林肯品牌乘用车、卡车及商用车，并布局电动化与自动驾驶技术。</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>采购汽车制造产线机器人（焊接、喷涂、装配）、AGV/AMR物流机器人、视觉检测系统及自动化集成设备。</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备汽车行业产线自动化集成经验、通过IATF 16949认证、能提供本地化服务与快速响应的中国设备供应商。</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、英国、德国、中国</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>福特中国（上海）有限公司，南京工程研发中心</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>通用汽车、丰田汽车、Stellantis</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>美国汽车市场份额约13%，全球约5%</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布投资30亿美元扩建田纳西州电动皮卡工厂，引入新一代柔性自动化产线。</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
           <t>Automotive OEM</t>
         </is>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="n">
         <v>85</v>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>High-volume manufacturing with intense cost pressure and a history of sourcing global automation to stay competitive.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Ford%20Motor%20Company</t>
         </is>
       </c>
     </row>
@@ -679,35 +884,85 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1957</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>奥罗拉，加拿大</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>179000</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>428亿美元</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>全球第三大汽车零部件供应商，提供车身、底盘、外饰、座椅、动力总成及整车代工服务。</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>采购汽车零部件焊接/装配机器人工作站、视觉引导抓取系统、自动化检测设备及智能拧紧系统。</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>需要具备汽车零部件行业案例、能提供交钥匙工程、具备全球化服务网络的中国自动化集成商。</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>美国、德国、中国、墨西哥、韩国</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>麦格纳汽车系统（上海）有限公司，在华拥有多个工厂</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>博世、采埃孚、佛瑞亚</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>全球汽车零部件供应商排名第3，北美市场份额约15%</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>2025年获得某欧洲豪华品牌电动车平台电池壳体订单，投资新建自动化产线。</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
           <t>Tier 1 supplier</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="n">
         <v>82</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Canada</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>Global Tier 1 with thin margins and high volume, constantly seeking lower-cost automation for assembly and welding.</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Magna%20International%20Inc.</t>
         </is>
       </c>
     </row>
@@ -724,35 +979,85 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>沃尔夫斯堡，德国</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>684000</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3220亿欧元</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>欧洲最大汽车集团，旗下拥有大众、奥迪、保时捷、斯柯达等品牌，覆盖乘用车、商用车及金融服务。</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>采购整车及零部件产线机器人、动力电池装配自动化设备、智能仓储物流系统及工业4.0解决方案。</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>偏好具有欧洲项目交付经验、熟悉CE认证、能提供模块化自动化单元和数字化工厂解决方案的中国供应商。</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>德国、中国、美国、巴西、墨西哥</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>大众汽车（中国）投资有限公司，合肥大众安徽工厂</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>丰田汽车、Stellantis、现代汽车</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>全球汽车销量约11%，欧洲市场占有率约25%</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>2025年与地平线合作开发智能驾驶域控制器，同时加速中国区电动化产线改造。</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>Automotive OEM</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>Massive global production footprint and ongoing EV transition require cost-effective automation solutions.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Volkswagen%20AG</t>
         </is>
       </c>
     </row>
@@ -769,35 +1074,85 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>水原市，韩国</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>270000</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2000亿美元</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的消费电子与半导体制造商，产品涵盖智能手机、电视、存储芯片及家用电器。</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>需要采购用于半导体产线、电子产品装配的精密工业机器人、AGV/AMR及视觉检测自动化设备。</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备半导体/电子行业案例、高精度控制能力、可提供全球售后服务的自动化集成商与设备供应商。</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>韩国、美国、中国、印度、越南</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>苏州、深圳、西安设有生产基地及研发中心</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Apple, Intel, LG Electronics</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>全球智能手机市场份额约20%，半导体存储市场份额约40%</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在韩国平泽新建先进半导体封装线，引入全自动化物流系统。</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
           <t>Electronics manufacturer</t>
         </is>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>High-volume electronics assembly with extreme cost sensitivity and existing supply chain ties to China.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Samsung%20Electronics%20Co.%2C%20Ltd.</t>
         </is>
       </c>
     </row>
@@ -814,35 +1169,85 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1886</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>斯图加特，德国</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>421000</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>916亿欧元</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的技术与服务供应商，业务涵盖汽车与智能交通技术、工业技术、消费品及能源与建筑技术。</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>采购精密装配机器人、传感器自动化生产线、电子元件贴装与检测设备、工业机器人控制器及驱动系统。</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>寻求在精密电子制造自动化领域有专长、通过ISO 9001/14001认证、具备联合研发能力的中国供应商。</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>德国、中国、美国、印度、日本</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>博世（中国）投资有限公司，苏州、南京、长沙设有工厂</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>大陆集团、电装、西门子</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>全球汽车零部件供应商排名第1，汽车电子市场份额约20%</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布投资10亿欧元在苏州建设新能源汽车核心部件自动化工厂。</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
           <t>Tier 1 supplier</t>
         </is>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>Diverse manufacturing operations and cost optimization initiatives make them a candidate for Chinese robots in secondary processes.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Robert%20Bosch%20GmbH</t>
         </is>
       </c>
     </row>
@@ -859,35 +1264,85 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>底特律，美国</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>164000</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>约1700亿美元</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>美国最大汽车制造商，旗下雪佛兰、凯迪拉克等品牌，正全面转型电动化，在北美及全球工厂大规模部署机器人焊接、涂装和电池装配线。</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购电池模组PACK自动化产线、机器人末端执行器、视觉引导系统及冲压自动化周边设备。</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>偏好有汽车OEM一级供应商经验、具备国际化交付能力（北美/墨西哥建点）的中国设备商，重视安全认证和售后响应。</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、中国、墨西哥、巴西</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>通用汽车（中国）投资有限公司，上海总部，另在武汉/沈阳有合资工厂</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>福特汽车、丰田汽车、大众汽车</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>全球汽车市场份额约6%（2025年），美国本土市场份额约16%。</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布与宁德时代合作，在北美新建电池工厂，并同步采购中国产自动化装配线。</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
           <t>Automotive OEM</t>
         </is>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>GM's aggressive EV investment and cost-cutting initiatives make them a strong candidate for lower-cost Chinese robots in body shops.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=General%20Motors%20Company</t>
         </is>
       </c>
     </row>
@@ -904,35 +1359,85 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1937</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>丰田市，日本</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>375000</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3100亿美元</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>全球最大汽车制造商之一，以精益生产著称，产品涵盖混动、纯电、氢燃料电池车及商用车。</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>采购高精度装配机器人、柔性制造单元、质量检测自动化设备及人机协作机器人。</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>寻找能适应丰田精益生产体系（TPS）、具备高良率设备制造能力、愿意深度定制化开发的中国合作伙伴。</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>日本、美国、中国、泰国、印度尼西亚</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>丰田汽车（中国）投资有限公司，常熟研发中心</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>大众汽车、本田汽车、现代汽车</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>全球汽车销量约12%，日本国内市场份额约45%</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在九州新建电池工厂，导入全自动电极与组装产线。</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>Automotive OEM</t>
         </is>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>Lean manufacturing and cost discipline make them open to competitive Chinese robotics for non-core tasks.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Toyota%20Motor%20Corporation</t>
         </is>
       </c>
     </row>
@@ -949,35 +1454,85 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1935</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>美国阿肯色州斯普林代尔</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>139000</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>约533亿美元</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>全球最大的肉类及禽类加工企业之一，销售鸡肉、牛肉、猪肉及预制食品，旗下拥有Jimmy Dean、Hillshire Farm等品牌。</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>需要采购肉类加工自动化设备，如智能分割机器人、自动去骨系统、视觉检测与分拣机器人、包装自动化流水线。</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>寻找有食品加工行业经验、能提供定制化机器人解决方案、具备北美服务能力且符合食品安全认证（如NSF/CE）的供应商。</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>美国、中国、墨西哥、加拿大、英国</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>在上海设有办事处，并在中国有合资工厂（如江苏泰森食品）。</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>JBS S.A.、Cargill Protein、Pilgrim's Pride</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>美国鸡肉市场份额约20%，牛肉约15%，为美国最大肉类生产商之一。</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布投资2亿美元在田纳西州新建自动化鸡肉加工厂，采用AI视觉和机器人切割技术。</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>Food processing</t>
         </is>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="S11" s="2" t="inlineStr">
         <is>
           <t>Labor shortages and high turnover in meat processing push them to adopt affordable automation, including Chinese robots.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Tyson%20Foods%2C%20Inc.</t>
         </is>
       </c>
     </row>
@@ -994,35 +1549,85 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1866</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>沃韦，瑞士</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>270000</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>930亿瑞士法郎</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>全球最大食品饮料公司，产品涵盖咖啡、乳制品、宠物食品、瓶装水等。</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>采购食品级包装自动化设备、高速分拣机器人、码垛机器人及食品生产线视觉检测系统。</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>需要符合食品卫生标准（FDA/EU）、具备食品行业案例、能提供无菌环境自动化方案的供应商。</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>美国、中国、巴西、德国、印度</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>北京、上海、东莞、青岛等地设有30余家工厂</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>PepsiCo, Unilever, Kraft Heinz</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>全球包装食品市场份额约5%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布投资5亿瑞士法郎升级欧洲工厂，全面部署协作机器人用于包装线。</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>Food processing</t>
         </is>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland (US operations)</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Switzerland (US operations)</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="S12" s="2" t="inlineStr">
         <is>
           <t>Food packaging and palletizing are repetitive tasks where Chinese robots offer significant cost savings over European brands.</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nestl%C3%A9%20S.A.</t>
         </is>
       </c>
     </row>
@@ -1039,35 +1644,85 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>首尔，韩国</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>72000</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>约1200亿美元</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>韩国最大汽车制造商，近年大力投资机器人技术（波士顿动力母公司），在汽车制造产线中大规模部署工业机器人及智能物流设备。</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购汽车焊装机器人配套夹具、AGV小车、视觉检测系统、以及电池产线自动化设备。</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>寻求具备汽车行业项目经验、能提供交钥匙工程的中国自动化集成商，要求有全球服务能力和成本竞争力。</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>美国、韩国、中国、印度、欧洲</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>现代汽车（中国）投资有限公司，北京/上海/烟台设有研发及采购中心</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>丰田汽车、大众汽车、特斯拉</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>全球汽车市场份额约4.5%（2025年），在韩国本土市场份额第一。</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布与现代重工合作，在韩国蔚山工厂引入中国产协作机器人进行零部件装配试点。</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>Automotive OEM</t>
         </is>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>Korean automakers face cost competition and have been increasing automation in their plants, with potential to test Chinese robots.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Hyundai%20Motor%20Company</t>
         </is>
       </c>
     </row>
@@ -1084,35 +1739,85 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1969</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>波恩，德国</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>400000</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>800亿欧元</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的合同物流与供应链解决方案提供商，提供仓储、运输、配送及增值服务。</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>采购仓储自动化设备，包括AGV/AMR、自动分拣系统、机械臂码垛机及WMS/WCS软件集成方案。</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>寻找有大型物流中心成功案例、可提供软硬件一体化方案、具备全球部署能力的自动化设备厂商。</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>德国、美国、中国、英国、荷兰</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>上海、香港设有亚太区总部及多个物流中心</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Kuehne+Nagel, DB Schenker, XPO Logistics</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>全球合同物流市场份额约10%</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在德国莱比锡枢纽部署500台自主移动机器人，提升包裹分拣效率。</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
           <t>3PL logistics</t>
         </is>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>Warehouse automation is a priority, and Chinese AMRs and robotic arms offer cost-effective solutions for sorting and packing.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=DHL%20Supply%20Chain</t>
         </is>
       </c>
     </row>
@@ -1129,35 +1834,85 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>美国北卡罗来纳州夏洛特</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>32000</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>约350亿美元</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>美国最大的钢铁生产商（以电弧炉为主），销售钢材、钢板、钢梁、钢筋及钢管产品，同时生产钢铁加工设备。</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>需要采购钢铁产线自动化设备，如连铸连轧机器人、自动取样与检测系统、无人天车、智能物流与仓储自动化系统。</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>寻找有冶金行业自动化经验、能提供重载机器人及耐高温设备、具备北美本地服务能力的供应商。</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、墨西哥、巴西、欧洲</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>暂无正式分公司，但通过贸易商采购中国设备。</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Steel Dynamics Inc.、U.S. Steel、ArcelorMittal</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>美国粗钢产量市场份额约20%，为北美最大电弧炉钢企。</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在肯塔基州新建一座全自动化微型钢厂，采用AI控制轧制过程。</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
           <t>Metal fab</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="S15" s="2" t="inlineStr">
         <is>
           <t>Steel processing and material handling require robust robots, and Chinese vendors offer competitive pricing for high-volume use.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Nucor%20Corporation</t>
         </is>
       </c>
     </row>
@@ -1174,35 +1929,85 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>德国埃森</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>约350亿欧元</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>德国工业巨头，业务涵盖钢铁、电梯、汽车零部件、工业解决方案等，销售电梯系统、汽车转向系统、材料服务及工厂工程设备。</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>需要采购工业机器人（焊接、装配、搬运）、自动化输送系统、智能仓储设备、电梯部件装配机器人及检测设备。</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备工业4.0能力、有大型机械制造项目经验、能提供高精度机器人及自动化集成方案的中国供应商，要求有国际认证（CE/ISO）。</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>德国、美国、中国、印度、巴西</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>在中国设有多个生产基地和采购中心，如上海、常州、大连等。</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Siemens AG、Mitsubishi Heavy Industries、KONE Corporation</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>全球电梯市场排名前五，欧洲钢铁市场份额领先，但整体业务处于转型期。</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布剥离钢铁业务，聚焦于电梯和工业解决方案，并加大在自动化领域的投资。</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
           <t>Metal fab</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R16" s="5" t="n">
         <v>68</v>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Germany</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>Heavy metal fabrication and welding tasks are ideal for cost-effective Chinese industrial robots.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=ThyssenKrupp%20AG</t>
         </is>
       </c>
     </row>
@@ -1219,35 +2024,85 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1989</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>格林威治，美国</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100000</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>150亿美元</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>北美领先的物流运输与供应链服务公司，提供零担运输、货运经纪及最后一公里配送服务。</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>采购用于货运分拣的自动化设备、叉车AGV、输送线系统及车队管理自动化技术。</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>寻求能提供高性价比物流自动化设备、有北美市场服务经验、支持快速部署的供应商。</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>美国、加拿大、墨西哥、英国、法国</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>上海设有采购代表处</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>FedEx Logistics, UPS Supply Chain, C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>北美零担运输市场份额约8%</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出AI驱动的智能分拣中心，在德克萨斯州部署自动化装卸系统。</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
           <t>3PL logistics</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R17" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>Large-scale distribution centers need affordable robotic palletizing and picking solutions to compete with rivals.</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=XPO%20Logistics%2C%20Inc.</t>
         </is>
       </c>
     </row>
@@ -1264,35 +2119,85 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1903</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>密尔沃基，美国</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>约90亿美元</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的工业自动化和数字化转型企业，提供PLC、变频器、运动控制、工业网络及FactoryTalk软件平台，专注智能制造。</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购工业控制柜组件、PCB板、连接器、传感器、以及边缘计算硬件设备。</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>寻找具备电子制造服务（EMS）能力、有UL/CE认证、能提供ODM定制开发的中国合作伙伴，重视软件集成能力。</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>美国、中国、德国、印度、巴西</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>罗克韦尔自动化（中国）有限公司，上海总部，大连/深圳设有研发中心</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>西门子、施耐德电气、ABB</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>全球工业自动化市场份额约5%，在北美市场排名第一。</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布与中控技术合作，在中国推出本地化边缘控制解决方案，并加大在华采购力度。</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
           <t>System integrator</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R18" s="5" t="n">
         <v>65</v>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>They provide automation solutions and may integrate Chinese robots for cost-sensitive clients in North America.</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Rockwell%20Automation%2C%20Inc.</t>
         </is>
       </c>
     </row>
@@ -1309,35 +2214,85 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1956</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>山梨县忍野村，日本</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>8000</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>约7000亿日元（约50亿美元）</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>全球最大的工业机器人制造商之一，产品涵盖机器人、CNC数控系统、注塑机及工厂自动化解决方案，以高精度高可靠性著称。</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>需要从中国采购伺服电机零部件、精密铸件、线束组件、以及机器人控制柜的电子元器件。</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>偏好技术实力强、成本控制优秀、能配合严格质量审核（如FANUC认证）的长期战略供应商，尤其看重交货准时率。</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>日本、中国、美国、德国、泰国</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>上海发那科机器人有限公司（中国总部），另在广州、武汉设有基地</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>ABB、安川电机、库卡</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>全球工业机器人市场份额约17%，中国市场份额约15%（常年第一）。</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>2025年推出新一代协作机器人CRX系列，并宣布在中国扩大伺服电机本地采购比例至30%。</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>System integrator</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R19" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>They are a competitor, but they also buy components and could source Chinese robots for low-end applications in Asia.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=FANUC%20Corporation</t>
         </is>
       </c>
     </row>
@@ -1354,35 +2309,85 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1849</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>美国纽约州纽约市</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>88000</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>约580亿美元</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>全球领先的制药企业，销售处方药、疫苗（如Comirnaty新冠疫苗）和肿瘤药物，覆盖多个治疗领域。</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>需要采购制药自动化设备，如无菌灌装机器人、药品包装自动化线、实验室自动化系统、智能仓储与物流机器人。</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>寻找符合GMP/FDA认证、有制药行业洁净室自动化经验、能提供高精度和可追溯性系统的供应商。</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>美国、中国、日本、德国、英国</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>在上海设有研发中心，在大连和无锡有生产基地。</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Johnson &amp; Johnson、Roche、Merck &amp; Co.</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>全球处方药市场份额约5%，疫苗领域全球领先。</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布与AI公司合作，在爱尔兰工厂部署机器人进行药品包装和质检。</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R20" s="5" t="n">
         <v>55</v>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>Pharma automation is highly regulated, but secondary packaging and logistics could use Chinese robots for cost savings.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Pfizer%20Inc.</t>
         </is>
       </c>
     </row>
@@ -1399,118 +2404,90 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>瑞士巴塞尔</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>76000</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>约450亿美元</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>全球性医药健康公司，销售创新药、仿制药（Sandoz）、眼科产品及细胞基因疗法，专注于肿瘤、免疫和神经科学。</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>需要采购制药自动化设备，如高精度灌装机器人、无菌隔离器、自动视觉检测系统、实验室自动化及智能包装线。</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>寻找有制药行业GMP认证、能提供模块化自动化方案、具备全球服务网络和合规文档能力的中国供应商。</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>美国、中国、德国、日本、法国</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>在北京、上海设有研发中心，在苏州和中山有生产基地。</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Roche、AstraZeneca、Bristol-Myers Squibb</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>全球创新药市场份额约4%，在肿瘤和罕见病领域领先。</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2025年宣布在瑞士工厂引入协作机器人用于细胞治疗产品的自动化生产。</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
           <t>Pharma</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>Switzerland (US operations)</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>Enterprise (&gt;1000)</t>
+        </is>
+      </c>
+      <c r="R21" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Enterprise (&gt;1000)</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Switzerland (US operations)</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>Regulatory hurdles limit core production, but warehouse and lab automation could see Chinese robot adoption.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>No - no public record</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/search/results/companies/?keywords=Novartis%20International%20AG</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I21"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>Definition</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>90-95</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Top-tier — large scale, known to source from China</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>75-89</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Strong fit — cost-sensitive, growing demand</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>55-74</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Moderate fit — possible buyer</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>40-54</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Weak fit — niche or occasional</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A1:S21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>